--- a/OUTPUT/reverse_Q9A724_Caulobacter_crescentus_CB15.xlsx
+++ b/OUTPUT/reverse_Q9A724_Caulobacter_crescentus_CB15.xlsx
@@ -482,11 +482,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>TA</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.6948</v>
+        <v>0.6947221111555378</v>
       </c>
     </row>
   </sheetData>
